--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.3099</v>
+        <v>17.77811</v>
       </c>
       <c r="D2" t="n">
-        <v>17.15829</v>
+        <v>17.17843</v>
       </c>
       <c r="E2" t="n">
-        <v>17.20788</v>
+        <v>17.31995</v>
       </c>
       <c r="F2" t="n">
-        <v>44.34491</v>
+        <v>43.49206</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05246</v>
+        <v>0.05198</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8798</v>
+        <v>1.8542</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.14617</v>
+        <v>17.35992</v>
       </c>
       <c r="D3" t="n">
-        <v>17.32329</v>
+        <v>17.19211</v>
       </c>
       <c r="E3" t="n">
-        <v>17.03381</v>
+        <v>17.2396</v>
       </c>
       <c r="F3" t="n">
-        <v>43.49209</v>
+        <v>43.39147</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05241</v>
+        <v>0.05131</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84137</v>
+        <v>1.9032</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.11955</v>
+        <v>17.17857</v>
       </c>
       <c r="D4" t="n">
-        <v>17.31643</v>
+        <v>16.95548</v>
       </c>
       <c r="E4" t="n">
-        <v>16.99237</v>
+        <v>16.97931</v>
       </c>
       <c r="F4" t="n">
-        <v>43.51243</v>
+        <v>43.57865</v>
       </c>
       <c r="G4" t="n">
-        <v>0.052</v>
+        <v>0.05154</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85576</v>
+        <v>1.8653</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.30256</v>
+        <v>17.25698</v>
       </c>
       <c r="D6" t="n">
-        <v>16.52094</v>
+        <v>16.65996</v>
       </c>
       <c r="E6" t="n">
-        <v>16.86641</v>
+        <v>17.07338</v>
       </c>
       <c r="F6" t="n">
-        <v>22.21045</v>
+        <v>22.68868</v>
       </c>
       <c r="G6" t="n">
-        <v>35.06122</v>
+        <v>35.35284</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.32613</v>
+        <v>17.16464</v>
       </c>
       <c r="D7" t="n">
-        <v>16.28041</v>
+        <v>16.8202</v>
       </c>
       <c r="E7" t="n">
-        <v>17.1951</v>
+        <v>16.84711</v>
       </c>
       <c r="F7" t="n">
-        <v>22.53803</v>
+        <v>22.23163</v>
       </c>
       <c r="G7" t="n">
-        <v>35.25922</v>
+        <v>35.3849</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.26325</v>
+        <v>17.50943</v>
       </c>
       <c r="D8" t="n">
-        <v>16.20931</v>
+        <v>16.39948</v>
       </c>
       <c r="E8" t="n">
-        <v>16.91172</v>
+        <v>16.67277</v>
       </c>
       <c r="F8" t="n">
-        <v>22.71903</v>
+        <v>22.53747</v>
       </c>
       <c r="G8" t="n">
-        <v>35.09417</v>
+        <v>35.98085</v>
       </c>
     </row>
   </sheetData>
